--- a/ARM Functions/Ability Edits/Neuroforce.xlsx
+++ b/ARM Functions/Ability Edits/Neuroforce.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A241285-B3C6-4A60-935C-5BE706499408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06008AEC-A55F-422B-9811-CB67C4E32361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="377" yWindow="377" windowWidth="24686" windowHeight="13149" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="1232">
   <si>
     <t>Address</t>
   </si>
@@ -3565,15 +3565,6 @@
     <t>Regenerator 0x6A</t>
   </si>
   <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>mov r0, 0x2</t>
-  </si>
-  <si>
-    <t>check self</t>
-  </si>
-  <si>
     <t>mov r1, 0x1</t>
   </si>
   <si>
@@ -3586,42 +3577,9 @@
     <t>1.2x SE damage 0x5B</t>
   </si>
   <si>
-    <t>10402DE9</t>
-  </si>
-  <si>
-    <t>push {r4, lr}</t>
-  </si>
-  <si>
     <t xml:space="preserve">bl 0x00087B58 </t>
   </si>
   <si>
-    <t>4900A0E3</t>
-  </si>
-  <si>
-    <t>mov r0, 0x49</t>
-  </si>
-  <si>
-    <t>Check if STAB</t>
-  </si>
-  <si>
-    <t>if STAB do nothing</t>
-  </si>
-  <si>
-    <t>061BA0E3</t>
-  </si>
-  <si>
-    <t>mov r1, 0x1800</t>
-  </si>
-  <si>
-    <t>3900A0E3</t>
-  </si>
-  <si>
-    <t>mov r0, 0x39</t>
-  </si>
-  <si>
-    <t>1040BDE8</t>
-  </si>
-  <si>
     <t>b 0x00082D44</t>
   </si>
   <si>
@@ -3631,84 +3589,15 @@
     <t>mov r0, 0x19</t>
   </si>
   <si>
-    <t>Get type</t>
-  </si>
-  <si>
-    <t>mov r0, 0x12</t>
-  </si>
-  <si>
-    <t>bl 0x000001D8</t>
-  </si>
-  <si>
-    <t>1200A0E3</t>
-  </si>
-  <si>
-    <t>Add STAB for Psychic, Poison, Fairy, Ghost 0x54</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x3</t>
-  </si>
-  <si>
-    <t>cmpne r0, 0xD</t>
-  </si>
-  <si>
-    <t>cmpne r0, 0x7</t>
-  </si>
-  <si>
-    <t>cmpne r0, 0x11</t>
-  </si>
-  <si>
     <t>000DDFA0</t>
   </si>
   <si>
-    <t>bne 0x000DDF9C</t>
-  </si>
-  <si>
-    <t>branching to previous pop from nearly-identical function to fit</t>
-  </si>
-  <si>
-    <t>E9A6FEEB</t>
-  </si>
-  <si>
-    <t>F8FFFF1A</t>
-  </si>
-  <si>
-    <t>E5A6FEEB</t>
-  </si>
-  <si>
-    <t>F4FFFF1A</t>
-  </si>
-  <si>
-    <t>E1A6FEEB</t>
-  </si>
-  <si>
-    <t>8088FCEB</t>
-  </si>
-  <si>
-    <t>030050E3</t>
-  </si>
-  <si>
-    <t>07005013</t>
-  </si>
-  <si>
-    <t>0D005013</t>
-  </si>
-  <si>
-    <t>ECFFFF1A</t>
-  </si>
-  <si>
-    <t>5293FEEA</t>
-  </si>
-  <si>
     <t>mov r0, 0x03</t>
   </si>
   <si>
     <t>Check Attacking</t>
   </si>
   <si>
-    <t>Check that Move Type is Poison</t>
-  </si>
-  <si>
     <t>1800A0E3</t>
   </si>
   <si>
@@ -3718,9 +3607,6 @@
     <t>get current Type (1/2 from phase 4E/4F)</t>
   </si>
   <si>
-    <t>Check that that Type is Steel</t>
-  </si>
-  <si>
     <t>7040BDE8</t>
   </si>
   <si>
@@ -3733,18 +3619,12 @@
     <t>mov r0, 0x50</t>
   </si>
   <si>
-    <t>NVE on Dark if Psychic 0x4E/0x4F</t>
-  </si>
-  <si>
     <t>cmp r0, 0xD</t>
   </si>
   <si>
     <t>cmp r0, 0x10</t>
   </si>
   <si>
-    <t>Make NVE</t>
-  </si>
-  <si>
     <t>bl 0x00082D44</t>
   </si>
   <si>
@@ -3785,6 +3665,75 @@
   </si>
   <si>
     <t>3D00A0E3</t>
+  </si>
+  <si>
+    <t>Make E</t>
+  </si>
+  <si>
+    <t>mov r1, 0x7</t>
+  </si>
+  <si>
+    <t>E on Dark if Psychic 0x4E/0x4F</t>
+  </si>
+  <si>
+    <t>Check that that Type is Dark</t>
+  </si>
+  <si>
+    <t>Check that Move Type is Psychic</t>
+  </si>
+  <si>
+    <t>Add STAB for Psychic, Poison, Fairy, Ghost 0x5B</t>
+  </si>
+  <si>
+    <t>0900A0E3</t>
+  </si>
+  <si>
+    <t>mov r0, 0x9</t>
+  </si>
+  <si>
+    <t>bl 0x001032EC</t>
+  </si>
+  <si>
+    <t>04E09DE4</t>
+  </si>
+  <si>
+    <t>0800A0E3</t>
+  </si>
+  <si>
+    <t>mov r0, 0x8</t>
+  </si>
+  <si>
+    <t>b 0x001032EC</t>
+  </si>
+  <si>
+    <t>push {lr}</t>
+  </si>
+  <si>
+    <t>mov r0, 0x11</t>
+  </si>
+  <si>
+    <t>mov r0, 0x7</t>
+  </si>
+  <si>
+    <t>04E02DE5</t>
+  </si>
+  <si>
+    <t>CF9400EB</t>
+  </si>
+  <si>
+    <t>CD9400EB</t>
+  </si>
+  <si>
+    <t>1100A0E3</t>
+  </si>
+  <si>
+    <t>CB9400EB</t>
+  </si>
+  <si>
+    <t>0700A0E3</t>
+  </si>
+  <si>
+    <t>C89400EA</t>
   </si>
 </sst>
 </file>
@@ -3888,7 +3837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3910,13 +3859,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -3932,6 +3874,8 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4266,7 +4210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultColWidth="9.0703125" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="8" customWidth="1"/>
@@ -4299,21 +4243,21 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="7" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="B2" s="9"/>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="C3" s="8" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(D3,1),"10A0E3")</f>
         <v>0110A0E3</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4374,7 +4318,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="12"/>
@@ -4382,7 +4326,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="8" t="s">
-        <v>1246</v>
+        <v>1206</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="12"/>
@@ -4390,631 +4334,465 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="8" t="s">
-        <v>1206</v>
+        <v>1183</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1182</v>
+        <v>1225</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1183</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="8" t="str">
-        <f t="shared" ref="A14:A34" si="1">DEC2HEX(HEX2DEC(A13)+4,8)</f>
+        <f t="shared" ref="A14:A18" si="1">DEC2HEX(HEX2DEC(A13)+4,8)</f>
         <v>000DDFA4</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>852</v>
+        <v>1215</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>829</v>
+        <v>1216</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="13" t="str">
+      <c r="A15" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DDFA8</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>869</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>1177</v>
+      <c r="B15" s="8" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="13" t="str">
+      <c r="A16" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DDFAC</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D16" s="13"/>
+      <c r="B16" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="13" t="str">
+      <c r="A17" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DDFB0</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>854</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>846</v>
-      </c>
-      <c r="D17" s="13"/>
+      <c r="B17" s="8" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f>C15</f>
+        <v>bl 0x001032EC</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="13" t="str">
+      <c r="A18" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DDFB4</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="28" customFormat="1">
+      <c r="A19" s="28" t="str">
+        <f t="shared" ref="A19:A22" si="2">DEC2HEX(HEX2DEC(A18)+4,8)</f>
+        <v>000DDFB8</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C19" s="28" t="str">
+        <f>C17</f>
+        <v>bl 0x001032EC</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="28" customFormat="1">
+      <c r="A20" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>000DDFBC</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C20" s="8" t="str">
+        <f>SUBSTITUTE(C13,"push","pop")</f>
+        <v>pop {lr}</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="28" customFormat="1">
+      <c r="A21" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>000DDFC0</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="28" customFormat="1">
+      <c r="A22" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>000DDFC4</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B25" t="s">
+        <v>850</v>
+      </c>
+      <c r="C25" t="s">
+        <v>831</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="str">
+        <f t="shared" ref="A26:A47" si="3">DEC2HEX(HEX2DEC(A25)+4,8)</f>
+        <v>000DE1C0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>852</v>
+      </c>
+      <c r="C26" t="s">
+        <v>829</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1C4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>859</v>
+      </c>
+      <c r="C27" t="s">
+        <v>830</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1C8</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>853</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1CC</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1D0</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>854</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="D30" s="13"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1D4</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C31" s="13" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$47)</f>
+        <v>bne 0x000DE214</v>
+      </c>
+      <c r="D31" s="13"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1D8</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1DC</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D33" s="15"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1E0</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D34" s="15"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1E4</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C35" s="15" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$47)</f>
+        <v>bne 0x000DE214</v>
+      </c>
+      <c r="D35" s="15"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1E8</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1EC</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D37" s="19"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1F0</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1F4</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C39" s="21" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$47)</f>
+        <v>bne 0x000DE214</v>
+      </c>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1F8</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>879</v>
+      </c>
+      <c r="C40" s="26" t="s">
         <v>1210</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D40" s="26" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE1FC</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C41" s="26" t="s">
         <v>1207</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFB8</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFBC</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D20" s="15"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFC0</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>855</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="D41" s="26"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE200</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D42" s="26"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE204</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C43" s="4" t="str">
+        <f>SUBSTITUTE(C25,"push","pop")</f>
+        <v>pop {r4, r5, r6, lr}</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE208</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="C44" s="25" t="s">
         <v>1175</v>
       </c>
-      <c r="D21" s="15"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFC4</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C22" s="15" t="str">
-        <f>C18</f>
-        <v>bne 0x000DDF9C</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFC8</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFCC</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D24" s="17"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFD0</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D25" s="17"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFD4</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFD8</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFDC</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFE0</v>
-      </c>
-      <c r="B29" s="18">
-        <v>11005013</v>
-      </c>
-      <c r="C29" s="17" t="s">
+      <c r="D44" s="23" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE20C</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D45" s="23"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>000DE210</v>
+      </c>
+      <c r="B46" s="24" t="s">
         <v>1205</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFE4</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C30" s="17" t="str">
-        <f>C18</f>
-        <v>bne 0x000DDF9C</v>
-      </c>
-      <c r="D30" s="17"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFE8</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFEC</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFF0</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C33" s="8" t="str">
-        <f>SUBSTITUTE(C13,"push","pop")</f>
-        <v>pop {r4, lr}</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DDFF4</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36"/>
-      <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B37" t="s">
-        <v>850</v>
-      </c>
-      <c r="C37" t="s">
-        <v>831</v>
-      </c>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="str">
-        <f t="shared" ref="A38:A59" si="2">DEC2HEX(HEX2DEC(A37)+4,8)</f>
-        <v>000DE1C0</v>
-      </c>
-      <c r="B38" t="s">
-        <v>852</v>
-      </c>
-      <c r="C38" t="s">
-        <v>829</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1C4</v>
-      </c>
-      <c r="B39" t="s">
-        <v>859</v>
-      </c>
-      <c r="C39" t="s">
-        <v>830</v>
-      </c>
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1C8</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1CC</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D41" s="20"/>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1D0</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>854</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>846</v>
-      </c>
-      <c r="D42" s="20"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1D4</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C43" s="20" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$59)</f>
-        <v>bne 0x000DE214</v>
-      </c>
-      <c r="D43" s="20"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1D8</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1DC</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D45" s="22"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1E0</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>1232</v>
-      </c>
-      <c r="D46" s="22"/>
+      <c r="C46" s="23" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D46" s="23"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1E4</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C47" s="22" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$59)</f>
-        <v>bne 0x000DE214</v>
-      </c>
-      <c r="D47" s="22"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1E8</v>
-      </c>
-      <c r="B48" s="27" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1EC</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D49" s="26"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1F0</v>
-      </c>
-      <c r="B50" s="29" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1F4</v>
-      </c>
-      <c r="B51" s="29" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C51" s="28" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$59)</f>
-        <v>bne 0x000DE214</v>
-      </c>
-      <c r="D51" s="28"/>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1F8</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D52" s="33" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE1FC</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C53" s="33" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D53" s="33"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE200</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C54" s="33" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D54" s="33"/>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE204</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C55" s="4" t="str">
-        <f>SUBSTITUTE(C37,"push","pop")</f>
-        <v>pop {r4, r5, r6, lr}</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE208</v>
-      </c>
-      <c r="B56" s="31" t="s">
-        <v>862</v>
-      </c>
-      <c r="C56" s="32" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D56" s="30" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE20C</v>
-      </c>
-      <c r="B57" s="31" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D57" s="30"/>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>000DE210</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D58" s="30"/>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="str">
-        <f t="shared" si="2"/>
+      <c r="A47" t="str">
+        <f t="shared" si="3"/>
         <v>000DE214</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B47" t="s">
         <v>857</v>
       </c>
-      <c r="C59" t="str">
-        <f>SUBSTITUTE(C55,"lr","pc")</f>
+      <c r="C47" t="str">
+        <f>SUBSTITUTE(C43,"lr","pc")</f>
         <v>pop {r4, r5, r6, pc}</v>
       </c>
-      <c r="D59"/>
+      <c r="D47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
